--- a/artfynd/A 24278-2023 artfynd.xlsx
+++ b/artfynd/A 24278-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24278-2023 artfynd.xlsx
+++ b/artfynd/A 24278-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -921,6 +921,254 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121857313</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57791</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Våtseröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>401026</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6202424</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallaröd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121857312</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57785</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Våtseröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>401026</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6202424</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallaröd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24278-2023 artfynd.xlsx
+++ b/artfynd/A 24278-2023 artfynd.xlsx
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121857313</v>
+        <v>121857312</v>
       </c>
       <c r="B4" t="n">
-        <v>57791</v>
+        <v>57785</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,26 +939,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121857312</v>
+        <v>121857313</v>
       </c>
       <c r="B5" t="n">
-        <v>57785</v>
+        <v>57791</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,26 +1063,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">

--- a/artfynd/A 24278-2023 artfynd.xlsx
+++ b/artfynd/A 24278-2023 artfynd.xlsx
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121857312</v>
+        <v>121857313</v>
       </c>
       <c r="B4" t="n">
-        <v>57785</v>
+        <v>57799</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,26 +939,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121857313</v>
+        <v>121857312</v>
       </c>
       <c r="B5" t="n">
-        <v>57791</v>
+        <v>57793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,26 +1063,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">

--- a/artfynd/A 24278-2023 artfynd.xlsx
+++ b/artfynd/A 24278-2023 artfynd.xlsx
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121857313</v>
+        <v>121857312</v>
       </c>
       <c r="B4" t="n">
-        <v>57799</v>
+        <v>57793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,26 +939,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121857312</v>
+        <v>121857313</v>
       </c>
       <c r="B5" t="n">
-        <v>57793</v>
+        <v>57799</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,26 +1063,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">

--- a/artfynd/A 24278-2023 artfynd.xlsx
+++ b/artfynd/A 24278-2023 artfynd.xlsx
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121857312</v>
+        <v>121857313</v>
       </c>
       <c r="B4" t="n">
-        <v>57793</v>
+        <v>57803</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,26 +939,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1047,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121857313</v>
+        <v>121857312</v>
       </c>
       <c r="B5" t="n">
-        <v>57799</v>
+        <v>57797</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,26 +1063,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">

--- a/artfynd/A 24278-2023 artfynd.xlsx
+++ b/artfynd/A 24278-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111304367</v>
+        <v>111304360</v>
       </c>
       <c r="B2" t="n">
-        <v>56414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,11 +710,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>401026.1840869313</v>
+        <v>401026</v>
       </c>
       <c r="R2" t="n">
-        <v>6202423.2600265</v>
+        <v>6202424</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118198974</v>
+        <v>111304367</v>
       </c>
       <c r="B3" t="n">
-        <v>56635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,16 +801,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,14 +820,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -881,22 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,49 +909,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121857313</v>
+        <v>111304363</v>
       </c>
       <c r="B4" t="n">
-        <v>57809</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1005,22 +986,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,15 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121857312</v>
+        <v>121857313</v>
       </c>
       <c r="B5" t="n">
-        <v>57803</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,26 +1039,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1134,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1168,6 +1144,125 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121857312</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Våtseröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>401026</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6202424</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallaröd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonny Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24278-2023 artfynd.xlsx
+++ b/artfynd/A 24278-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111304360</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111304367</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111304363</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121857313</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,8 +1288,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121857312</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>